--- a/excel_routes/route_HMB_JED_threats.xlsx
+++ b/excel_routes/route_HMB_JED_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973DE507-3838-4D6C-BED5-3FA255A10754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E82A67-8284-492F-BBC0-B412B8DA0BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="100">
   <si>
     <t>Date</t>
   </si>
@@ -66,24 +66,24 @@
     <t>SM-453</t>
   </si>
   <si>
+    <t>EgyptAir MS-663</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>EGP</t>
+  </si>
+  <si>
+    <t>28-AUG-26</t>
+  </si>
+  <si>
     <t>EgyptAir MS-673</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>EGP</t>
-  </si>
-  <si>
     <t>EgyptAir MS-665</t>
   </si>
   <si>
-    <t>EgyptAir MS-663</t>
-  </si>
-  <si>
-    <t>28-AUG-26</t>
-  </si>
-  <si>
     <t>EgyptAir MS-661</t>
   </si>
   <si>
@@ -93,6 +93,9 @@
     <t>flyadeal F3-780</t>
   </si>
   <si>
+    <t>EgyptAir MS-671</t>
+  </si>
+  <si>
     <t>02-SEP-26</t>
   </si>
   <si>
@@ -108,9 +111,6 @@
     <t>SM-967</t>
   </si>
   <si>
-    <t>EgyptAir MS-671</t>
-  </si>
-  <si>
     <t>EgyptAir MS-643</t>
   </si>
   <si>
@@ -129,16 +129,7 @@
     <t>EgyptAir MS-669</t>
   </si>
   <si>
-    <t>14-SEP-26</t>
-  </si>
-  <si>
-    <t>21-SEP-26</t>
-  </si>
-  <si>
-    <t>27-SEP-26</t>
-  </si>
-  <si>
-    <t>28-SEP-26</t>
+    <t>20-SEP-26</t>
   </si>
   <si>
     <t>04-OCT-26</t>
@@ -153,18 +144,12 @@
     <t>11-OCT-26</t>
   </si>
   <si>
-    <t>12-OCT-26</t>
-  </si>
-  <si>
-    <t>14-OCT-26</t>
+    <t>flynas XY-570</t>
   </si>
   <si>
     <t>18-OCT-26</t>
   </si>
   <si>
-    <t>19-OCT-26</t>
-  </si>
-  <si>
     <t>25-OCT-26</t>
   </si>
   <si>
@@ -174,13 +159,19 @@
     <t>28-OCT-26</t>
   </si>
   <si>
+    <t>flynas XY-572</t>
+  </si>
+  <si>
+    <t>flynas XY-590</t>
+  </si>
+  <si>
     <t>29-OCT-26</t>
   </si>
   <si>
     <t>30-OCT-26</t>
   </si>
   <si>
-    <t>flynas XY-1568</t>
+    <t>flynas XY-584</t>
   </si>
   <si>
     <t>31-OCT-26</t>
@@ -730,7 +721,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K239"/>
+  <dimension ref="A1:K230"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -817,22 +808,22 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2">
-        <v>11440</v>
+        <v>9720</v>
       </c>
       <c r="E3" s="2">
-        <v>12000</v>
+        <v>10088</v>
       </c>
       <c r="F3" s="2">
-        <v>-560</v>
+        <v>-368</v>
       </c>
       <c r="G3" s="2">
         <v>46</v>
@@ -852,22 +843,22 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2">
-        <v>11440</v>
+        <v>9720</v>
       </c>
       <c r="E4" s="2">
-        <v>12000</v>
+        <v>10088</v>
       </c>
       <c r="F4" s="2">
-        <v>-560</v>
+        <v>-368</v>
       </c>
       <c r="G4" s="2">
         <v>46</v>
@@ -887,22 +878,22 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D5" s="2">
         <v>9720</v>
       </c>
       <c r="E5" s="2">
-        <v>10089</v>
+        <v>10088</v>
       </c>
       <c r="F5" s="2">
-        <v>-369</v>
+        <v>-368</v>
       </c>
       <c r="G5" s="2">
         <v>46</v>
@@ -922,31 +913,31 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D6" s="2">
-        <v>9720</v>
+        <v>4901</v>
       </c>
       <c r="E6" s="2">
-        <v>10089</v>
+        <v>10921</v>
       </c>
       <c r="F6" s="2">
-        <v>-369</v>
+        <v>-6020</v>
       </c>
       <c r="G6" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2">
         <v>30</v>
       </c>
       <c r="I6" s="2">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>14</v>
@@ -957,22 +948,22 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" s="2">
         <v>9720</v>
       </c>
       <c r="E7" s="2">
-        <v>10089</v>
+        <v>10921</v>
       </c>
       <c r="F7" s="2">
-        <v>-369</v>
+        <v>-1201</v>
       </c>
       <c r="G7" s="2">
         <v>46</v>
@@ -998,25 +989,25 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D8" s="2">
-        <v>4901</v>
+        <v>9720</v>
       </c>
       <c r="E8" s="2">
         <v>10921</v>
       </c>
       <c r="F8" s="2">
-        <v>-6020</v>
+        <v>-1201</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2">
         <v>30</v>
       </c>
       <c r="I8" s="2">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>14</v>
@@ -1033,16 +1024,16 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D9" s="2">
-        <v>9720</v>
+        <v>10553</v>
       </c>
       <c r="E9" s="2">
         <v>10921</v>
       </c>
       <c r="F9" s="2">
-        <v>-1201</v>
+        <v>-368</v>
       </c>
       <c r="G9" s="2">
         <v>46</v>
@@ -1062,22 +1053,22 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D10" s="2">
-        <v>9720</v>
+        <v>8901</v>
       </c>
       <c r="E10" s="2">
-        <v>10921</v>
+        <v>9433</v>
       </c>
       <c r="F10" s="2">
-        <v>-1201</v>
+        <v>-532</v>
       </c>
       <c r="G10" s="2">
         <v>46</v>
@@ -1097,22 +1088,22 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D11" s="2">
-        <v>10553</v>
+        <v>8901</v>
       </c>
       <c r="E11" s="2">
-        <v>10921</v>
+        <v>9433</v>
       </c>
       <c r="F11" s="2">
-        <v>-368</v>
+        <v>-532</v>
       </c>
       <c r="G11" s="2">
         <v>46</v>
@@ -1132,22 +1123,22 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D12" s="2">
-        <v>8095</v>
+        <v>8901</v>
       </c>
       <c r="E12" s="2">
         <v>9433</v>
       </c>
       <c r="F12" s="2">
-        <v>-1338</v>
+        <v>-532</v>
       </c>
       <c r="G12" s="2">
         <v>46</v>
@@ -1167,13 +1158,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D13" s="2">
         <v>8901</v>
@@ -1202,22 +1193,22 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D14" s="2">
-        <v>8901</v>
+        <v>8095</v>
       </c>
       <c r="E14" s="2">
         <v>9433</v>
       </c>
       <c r="F14" s="2">
-        <v>-532</v>
+        <v>-1338</v>
       </c>
       <c r="G14" s="2">
         <v>46</v>
@@ -1237,22 +1228,22 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D15" s="2">
-        <v>8901</v>
+        <v>8095</v>
       </c>
       <c r="E15" s="2">
         <v>9433</v>
       </c>
       <c r="F15" s="2">
-        <v>-532</v>
+        <v>-1338</v>
       </c>
       <c r="G15" s="2">
         <v>46</v>
@@ -1272,22 +1263,22 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D16" s="2">
-        <v>8095</v>
+        <v>8901</v>
       </c>
       <c r="E16" s="2">
         <v>9433</v>
       </c>
       <c r="F16" s="2">
-        <v>-1338</v>
+        <v>-532</v>
       </c>
       <c r="G16" s="2">
         <v>46</v>
@@ -1307,22 +1298,22 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D17" s="2">
-        <v>8095</v>
+        <v>8901</v>
       </c>
       <c r="E17" s="2">
         <v>9433</v>
       </c>
       <c r="F17" s="2">
-        <v>-1338</v>
+        <v>-532</v>
       </c>
       <c r="G17" s="2">
         <v>46</v>
@@ -1342,13 +1333,13 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2">
         <v>8901</v>
@@ -1377,31 +1368,31 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D19" s="2">
-        <v>8901</v>
+        <v>10320</v>
       </c>
       <c r="E19" s="2">
         <v>9433</v>
       </c>
       <c r="F19" s="2">
-        <v>-532</v>
+        <v>887</v>
       </c>
       <c r="G19" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H19" s="2">
         <v>30</v>
       </c>
       <c r="I19" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>14</v>
@@ -1412,31 +1403,31 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" s="2">
-        <v>8901</v>
+        <v>8272</v>
       </c>
       <c r="E20" s="2">
-        <v>9433</v>
+        <v>7331</v>
       </c>
       <c r="F20" s="2">
-        <v>-532</v>
+        <v>941</v>
       </c>
       <c r="G20" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H20" s="2">
         <v>30</v>
       </c>
       <c r="I20" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>14</v>
@@ -1447,31 +1438,31 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2">
-        <v>10321</v>
+        <v>8095</v>
       </c>
       <c r="E21" s="2">
         <v>9433</v>
       </c>
       <c r="F21" s="2">
-        <v>888</v>
+        <v>-1338</v>
       </c>
       <c r="G21" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2">
         <v>30</v>
       </c>
       <c r="I21" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>14</v>
@@ -1482,31 +1473,31 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D22" s="2">
-        <v>8273</v>
+        <v>8901</v>
       </c>
       <c r="E22" s="2">
-        <v>7331</v>
+        <v>9433</v>
       </c>
       <c r="F22" s="2">
-        <v>942</v>
+        <v>-532</v>
       </c>
       <c r="G22" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2">
         <v>30</v>
       </c>
       <c r="I22" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>14</v>
@@ -1520,19 +1511,19 @@
         <v>32</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D23" s="2">
-        <v>8095</v>
+        <v>8901</v>
       </c>
       <c r="E23" s="2">
         <v>9433</v>
       </c>
       <c r="F23" s="2">
-        <v>-1338</v>
+        <v>-532</v>
       </c>
       <c r="G23" s="2">
         <v>46</v>
@@ -1555,28 +1546,28 @@
         <v>32</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D24" s="2">
-        <v>8901</v>
+        <v>8955</v>
       </c>
       <c r="E24" s="2">
         <v>9433</v>
       </c>
       <c r="F24" s="2">
-        <v>-532</v>
+        <v>-478</v>
       </c>
       <c r="G24" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H24" s="2">
         <v>30</v>
       </c>
       <c r="I24" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>14</v>
@@ -1587,31 +1578,31 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D25" s="2">
-        <v>8901</v>
+        <v>8955</v>
       </c>
       <c r="E25" s="2">
         <v>9433</v>
       </c>
       <c r="F25" s="2">
-        <v>-532</v>
+        <v>-478</v>
       </c>
       <c r="G25" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H25" s="2">
         <v>30</v>
       </c>
       <c r="I25" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>14</v>
@@ -1622,34 +1613,34 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D26" s="2">
-        <v>8955</v>
+        <v>5583</v>
       </c>
       <c r="E26" s="2">
-        <v>9433</v>
+        <v>21460</v>
       </c>
       <c r="F26" s="2">
-        <v>-478</v>
+        <v>-15877</v>
       </c>
       <c r="G26" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H26" s="2">
         <v>30</v>
       </c>
       <c r="I26" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>15</v>
@@ -1657,34 +1648,34 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D27" s="2">
-        <v>8273</v>
+        <v>8095</v>
       </c>
       <c r="E27" s="2">
-        <v>7331</v>
+        <v>21460</v>
       </c>
       <c r="F27" s="2">
-        <v>942</v>
+        <v>-13365</v>
       </c>
       <c r="G27" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2">
         <v>30</v>
       </c>
       <c r="I27" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>15</v>
@@ -1695,31 +1686,31 @@
         <v>35</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D28" s="2">
-        <v>8273</v>
+        <v>8095</v>
       </c>
       <c r="E28" s="2">
-        <v>7331</v>
+        <v>21460</v>
       </c>
       <c r="F28" s="2">
-        <v>942</v>
+        <v>-13365</v>
       </c>
       <c r="G28" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2">
         <v>30</v>
       </c>
       <c r="I28" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>15</v>
@@ -1727,34 +1718,34 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D29" s="2">
-        <v>8955</v>
+        <v>8901</v>
       </c>
       <c r="E29" s="2">
-        <v>9433</v>
+        <v>21460</v>
       </c>
       <c r="F29" s="2">
-        <v>-478</v>
+        <v>-12559</v>
       </c>
       <c r="G29" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2">
         <v>30</v>
       </c>
       <c r="I29" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>15</v>
@@ -1771,13 +1762,13 @@
         <v>29</v>
       </c>
       <c r="D30" s="2">
-        <v>8273</v>
+        <v>7986</v>
       </c>
       <c r="E30" s="2">
         <v>7331</v>
       </c>
       <c r="F30" s="2">
-        <v>942</v>
+        <v>655</v>
       </c>
       <c r="G30" s="2">
         <v>40</v>
@@ -1800,19 +1791,19 @@
         <v>38</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D31" s="2">
-        <v>5870</v>
+        <v>5583</v>
       </c>
       <c r="E31" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F31" s="2">
-        <v>-15591</v>
+        <v>-15877</v>
       </c>
       <c r="G31" s="2">
         <v>0</v>
@@ -1824,7 +1815,7 @@
         <v>30</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>15</v>
@@ -1835,31 +1826,31 @@
         <v>38</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D32" s="2">
-        <v>8095</v>
+        <v>7290</v>
       </c>
       <c r="E32" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F32" s="2">
-        <v>-13366</v>
+        <v>-14170</v>
       </c>
       <c r="G32" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H32" s="2">
         <v>30</v>
       </c>
       <c r="I32" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>15</v>
@@ -1870,19 +1861,19 @@
         <v>38</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D33" s="2">
         <v>8095</v>
       </c>
       <c r="E33" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F33" s="2">
-        <v>-13366</v>
+        <v>-13365</v>
       </c>
       <c r="G33" s="2">
         <v>46</v>
@@ -1894,7 +1885,7 @@
         <v>-16</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>15</v>
@@ -1905,19 +1896,19 @@
         <v>38</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D34" s="2">
-        <v>8901</v>
+        <v>8095</v>
       </c>
       <c r="E34" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F34" s="2">
-        <v>-12560</v>
+        <v>-13365</v>
       </c>
       <c r="G34" s="2">
         <v>46</v>
@@ -1929,7 +1920,7 @@
         <v>-16</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>15</v>
@@ -1940,31 +1931,31 @@
         <v>40</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="2">
-        <v>8273</v>
+        <v>5583</v>
       </c>
       <c r="E35" s="2">
-        <v>7331</v>
+        <v>21460</v>
       </c>
       <c r="F35" s="2">
-        <v>942</v>
+        <v>-15877</v>
       </c>
       <c r="G35" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H35" s="2">
         <v>30</v>
       </c>
       <c r="I35" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>15</v>
@@ -1972,34 +1963,34 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D36" s="2">
-        <v>5870</v>
+        <v>8095</v>
       </c>
       <c r="E36" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F36" s="2">
-        <v>-15591</v>
+        <v>-13365</v>
       </c>
       <c r="G36" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H36" s="2">
         <v>30</v>
       </c>
       <c r="I36" s="2">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>15</v>
@@ -2007,22 +1998,22 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D37" s="2">
         <v>8095</v>
       </c>
       <c r="E37" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F37" s="2">
-        <v>-13366</v>
+        <v>-13365</v>
       </c>
       <c r="G37" s="2">
         <v>46</v>
@@ -2034,7 +2025,7 @@
         <v>-16</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>15</v>
@@ -2042,22 +2033,22 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D38" s="2">
-        <v>8095</v>
+        <v>8901</v>
       </c>
       <c r="E38" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F38" s="2">
-        <v>-13366</v>
+        <v>-12559</v>
       </c>
       <c r="G38" s="2">
         <v>46</v>
@@ -2069,7 +2060,7 @@
         <v>-16</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>15</v>
@@ -2080,31 +2071,31 @@
         <v>41</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D39" s="2">
-        <v>8901</v>
+        <v>5583</v>
       </c>
       <c r="E39" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F39" s="2">
-        <v>-12560</v>
+        <v>-15877</v>
       </c>
       <c r="G39" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H39" s="2">
         <v>30</v>
       </c>
       <c r="I39" s="2">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>15</v>
@@ -2112,34 +2103,34 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D40" s="2">
-        <v>8273</v>
+        <v>8095</v>
       </c>
       <c r="E40" s="2">
-        <v>7331</v>
+        <v>21460</v>
       </c>
       <c r="F40" s="2">
-        <v>942</v>
+        <v>-13365</v>
       </c>
       <c r="G40" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H40" s="2">
         <v>30</v>
       </c>
       <c r="I40" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>15</v>
@@ -2147,34 +2138,34 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D41" s="2">
-        <v>8273</v>
+        <v>8901</v>
       </c>
       <c r="E41" s="2">
-        <v>7331</v>
+        <v>21460</v>
       </c>
       <c r="F41" s="2">
-        <v>942</v>
+        <v>-12559</v>
       </c>
       <c r="G41" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H41" s="2">
         <v>30</v>
       </c>
       <c r="I41" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>15</v>
@@ -2182,34 +2173,34 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D42" s="2">
-        <v>5870</v>
+        <v>8901</v>
       </c>
       <c r="E42" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F42" s="2">
-        <v>-15591</v>
+        <v>-12559</v>
       </c>
       <c r="G42" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H42" s="2">
         <v>30</v>
       </c>
       <c r="I42" s="2">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>15</v>
@@ -2217,34 +2208,34 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D43" s="2">
-        <v>8095</v>
+        <v>4628</v>
       </c>
       <c r="E43" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F43" s="2">
-        <v>-13366</v>
+        <v>-16832</v>
       </c>
       <c r="G43" s="2">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H43" s="2">
         <v>30</v>
       </c>
       <c r="I43" s="2">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>15</v>
@@ -2252,34 +2243,34 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="D44" s="2">
-        <v>8095</v>
+        <v>4628</v>
       </c>
       <c r="E44" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F44" s="2">
-        <v>-13366</v>
+        <v>-16832</v>
       </c>
       <c r="G44" s="2">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H44" s="2">
         <v>30</v>
       </c>
       <c r="I44" s="2">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>15</v>
@@ -2287,34 +2278,34 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D45" s="2">
-        <v>8901</v>
+        <v>4628</v>
       </c>
       <c r="E45" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F45" s="2">
-        <v>-12560</v>
+        <v>-16832</v>
       </c>
       <c r="G45" s="2">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H45" s="2">
         <v>30</v>
       </c>
       <c r="I45" s="2">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>15</v>
@@ -2322,34 +2313,34 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D46" s="2">
-        <v>8273</v>
+        <v>5583</v>
       </c>
       <c r="E46" s="2">
-        <v>7331</v>
+        <v>21460</v>
       </c>
       <c r="F46" s="2">
-        <v>942</v>
+        <v>-15877</v>
       </c>
       <c r="G46" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H46" s="2">
         <v>30</v>
       </c>
       <c r="I46" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>15</v>
@@ -2360,31 +2351,31 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D47" s="2">
-        <v>5870</v>
+        <v>8901</v>
       </c>
       <c r="E47" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F47" s="2">
-        <v>-15591</v>
+        <v>-12559</v>
       </c>
       <c r="G47" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H47" s="2">
         <v>30</v>
       </c>
       <c r="I47" s="2">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>15</v>
@@ -2395,19 +2386,19 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D48" s="2">
-        <v>8095</v>
+        <v>8901</v>
       </c>
       <c r="E48" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F48" s="2">
-        <v>-13366</v>
+        <v>-12559</v>
       </c>
       <c r="G48" s="2">
         <v>46</v>
@@ -2419,7 +2410,7 @@
         <v>-16</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>15</v>
@@ -2430,19 +2421,19 @@
         <v>46</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D49" s="2">
         <v>8901</v>
       </c>
       <c r="E49" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F49" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G49" s="2">
         <v>46</v>
@@ -2454,7 +2445,7 @@
         <v>-16</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>15</v>
@@ -2462,34 +2453,34 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D50" s="2">
-        <v>8901</v>
+        <v>4628</v>
       </c>
       <c r="E50" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F50" s="2">
-        <v>-12560</v>
+        <v>-16832</v>
       </c>
       <c r="G50" s="2">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H50" s="2">
         <v>30</v>
       </c>
       <c r="I50" s="2">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>15</v>
@@ -2497,22 +2488,22 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D51" s="2">
-        <v>5870</v>
+        <v>5583</v>
       </c>
       <c r="E51" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F51" s="2">
-        <v>-15591</v>
+        <v>-15877</v>
       </c>
       <c r="G51" s="2">
         <v>0</v>
@@ -2524,7 +2515,7 @@
         <v>30</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>15</v>
@@ -2532,34 +2523,34 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D52" s="2">
-        <v>6157</v>
+        <v>8095</v>
       </c>
       <c r="E52" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F52" s="2">
-        <v>-15304</v>
+        <v>-13365</v>
       </c>
       <c r="G52" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H52" s="2">
         <v>30</v>
       </c>
       <c r="I52" s="2">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>15</v>
@@ -2567,34 +2558,34 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D53" s="2">
-        <v>6157</v>
+        <v>8901</v>
       </c>
       <c r="E53" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F53" s="2">
-        <v>-15304</v>
+        <v>-12559</v>
       </c>
       <c r="G53" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H53" s="2">
         <v>30</v>
       </c>
       <c r="I53" s="2">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>15</v>
@@ -2602,34 +2593,34 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D54" s="2">
-        <v>6157</v>
+        <v>5720</v>
       </c>
       <c r="E54" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F54" s="2">
-        <v>-15304</v>
+        <v>-15740</v>
       </c>
       <c r="G54" s="2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H54" s="2">
         <v>30</v>
       </c>
       <c r="I54" s="2">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>15</v>
@@ -2640,31 +2631,31 @@
         <v>49</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D55" s="2">
-        <v>8901</v>
+        <v>6157</v>
       </c>
       <c r="E55" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F55" s="2">
-        <v>-12560</v>
+        <v>-15303</v>
       </c>
       <c r="G55" s="2">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H55" s="2">
         <v>30</v>
       </c>
       <c r="I55" s="2">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>15</v>
@@ -2675,19 +2666,19 @@
         <v>49</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D56" s="2">
-        <v>8901</v>
+        <v>8095</v>
       </c>
       <c r="E56" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F56" s="2">
-        <v>-12560</v>
+        <v>-13365</v>
       </c>
       <c r="G56" s="2">
         <v>46</v>
@@ -2699,7 +2690,7 @@
         <v>-16</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>15</v>
@@ -2710,19 +2701,19 @@
         <v>49</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D57" s="2">
         <v>8901</v>
       </c>
       <c r="E57" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F57" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G57" s="2">
         <v>46</v>
@@ -2734,7 +2725,7 @@
         <v>-16</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>15</v>
@@ -2742,34 +2733,34 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D58" s="2">
-        <v>6157</v>
+        <v>5870</v>
       </c>
       <c r="E58" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F58" s="2">
-        <v>-15304</v>
+        <v>-15590</v>
       </c>
       <c r="G58" s="2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H58" s="2">
         <v>30</v>
       </c>
       <c r="I58" s="2">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>15</v>
@@ -2777,34 +2768,34 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="D59" s="2">
-        <v>7972</v>
+        <v>6157</v>
       </c>
       <c r="E59" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F59" s="2">
-        <v>-13489</v>
+        <v>-15303</v>
       </c>
       <c r="G59" s="2">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H59" s="2">
         <v>30</v>
       </c>
       <c r="I59" s="2">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>15</v>
@@ -2812,34 +2803,34 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D60" s="2">
-        <v>8273</v>
+        <v>6157</v>
       </c>
       <c r="E60" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F60" s="2">
-        <v>-13188</v>
+        <v>-15303</v>
       </c>
       <c r="G60" s="2">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H60" s="2">
         <v>30</v>
       </c>
       <c r="I60" s="2">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>15</v>
@@ -2847,22 +2838,22 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D61" s="2">
         <v>8901</v>
       </c>
       <c r="E61" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F61" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G61" s="2">
         <v>46</v>
@@ -2874,7 +2865,7 @@
         <v>-16</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>15</v>
@@ -2885,31 +2876,31 @@
         <v>52</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D62" s="2">
-        <v>5720</v>
+        <v>8901</v>
       </c>
       <c r="E62" s="2">
-        <v>21461</v>
+        <v>9433</v>
       </c>
       <c r="F62" s="2">
-        <v>-15741</v>
+        <v>-532</v>
       </c>
       <c r="G62" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H62" s="2">
         <v>30</v>
       </c>
       <c r="I62" s="2">
-        <v>30</v>
-      </c>
-      <c r="J62" s="4" t="s">
-        <v>39</v>
+        <v>-16</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>15</v>
@@ -2920,31 +2911,31 @@
         <v>52</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="D63" s="2">
-        <v>6157</v>
+        <v>8901</v>
       </c>
       <c r="E63" s="2">
-        <v>21461</v>
+        <v>9433</v>
       </c>
       <c r="F63" s="2">
-        <v>-15304</v>
+        <v>-532</v>
       </c>
       <c r="G63" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H63" s="2">
         <v>30</v>
       </c>
       <c r="I63" s="2">
-        <v>7</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>39</v>
+        <v>-16</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>15</v>
@@ -2952,34 +2943,34 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D64" s="2">
-        <v>8095</v>
+        <v>5870</v>
       </c>
       <c r="E64" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F64" s="2">
-        <v>-13366</v>
+        <v>-15590</v>
       </c>
       <c r="G64" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H64" s="2">
         <v>30</v>
       </c>
       <c r="I64" s="2">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>15</v>
@@ -2987,34 +2978,34 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="D65" s="2">
-        <v>8901</v>
+        <v>6157</v>
       </c>
       <c r="E65" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F65" s="2">
-        <v>-12560</v>
+        <v>-15303</v>
       </c>
       <c r="G65" s="2">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H65" s="2">
         <v>30</v>
       </c>
       <c r="I65" s="2">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>15</v>
@@ -3022,34 +3013,34 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D66" s="2">
-        <v>5870</v>
+        <v>6157</v>
       </c>
       <c r="E66" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F66" s="2">
-        <v>-15591</v>
+        <v>-15303</v>
       </c>
       <c r="G66" s="2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H66" s="2">
         <v>30</v>
       </c>
       <c r="I66" s="2">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>15</v>
@@ -3057,34 +3048,34 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="D67" s="2">
-        <v>6157</v>
+        <v>8095</v>
       </c>
       <c r="E67" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F67" s="2">
-        <v>-15304</v>
+        <v>-13365</v>
       </c>
       <c r="G67" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H67" s="2">
         <v>30</v>
       </c>
       <c r="I67" s="2">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>15</v>
@@ -3095,19 +3086,19 @@
         <v>54</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D68" s="2">
         <v>6157</v>
       </c>
       <c r="E68" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F68" s="2">
-        <v>-15304</v>
+        <v>-15303</v>
       </c>
       <c r="G68" s="2">
         <v>23</v>
@@ -3119,7 +3110,7 @@
         <v>7</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>15</v>
@@ -3130,31 +3121,31 @@
         <v>54</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D69" s="2">
-        <v>8901</v>
+        <v>6157</v>
       </c>
       <c r="E69" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F69" s="2">
-        <v>-12560</v>
+        <v>-15303</v>
       </c>
       <c r="G69" s="2">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H69" s="2">
         <v>30</v>
       </c>
       <c r="I69" s="2">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>15</v>
@@ -3162,22 +3153,22 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D70" s="2">
-        <v>8901</v>
+        <v>8095</v>
       </c>
       <c r="E70" s="2">
-        <v>9433</v>
+        <v>21460</v>
       </c>
       <c r="F70" s="2">
-        <v>-532</v>
+        <v>-13365</v>
       </c>
       <c r="G70" s="2">
         <v>46</v>
@@ -3188,8 +3179,8 @@
       <c r="I70" s="2">
         <v>-16</v>
       </c>
-      <c r="J70" s="3" t="s">
-        <v>14</v>
+      <c r="J70" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>15</v>
@@ -3200,31 +3191,31 @@
         <v>55</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D71" s="2">
-        <v>8901</v>
+        <v>5870</v>
       </c>
       <c r="E71" s="2">
-        <v>9433</v>
+        <v>21460</v>
       </c>
       <c r="F71" s="2">
-        <v>-532</v>
+        <v>-15590</v>
       </c>
       <c r="G71" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H71" s="2">
         <v>30</v>
       </c>
       <c r="I71" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>15</v>
@@ -3232,22 +3223,22 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D72" s="2">
         <v>6157</v>
       </c>
       <c r="E72" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F72" s="2">
-        <v>-15304</v>
+        <v>-15303</v>
       </c>
       <c r="G72" s="2">
         <v>23</v>
@@ -3259,7 +3250,7 @@
         <v>7</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>15</v>
@@ -3267,34 +3258,34 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D73" s="2">
-        <v>6157</v>
+        <v>8095</v>
       </c>
       <c r="E73" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F73" s="2">
-        <v>-15304</v>
+        <v>-13365</v>
       </c>
       <c r="G73" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H73" s="2">
         <v>30</v>
       </c>
       <c r="I73" s="2">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>15</v>
@@ -3302,34 +3293,34 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D74" s="2">
-        <v>6157</v>
+        <v>8901</v>
       </c>
       <c r="E74" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F74" s="2">
-        <v>-15304</v>
+        <v>-12559</v>
       </c>
       <c r="G74" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H74" s="2">
         <v>30</v>
       </c>
       <c r="I74" s="2">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>15</v>
@@ -3340,31 +3331,31 @@
         <v>56</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D75" s="2">
-        <v>8273</v>
+        <v>5720</v>
       </c>
       <c r="E75" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F75" s="2">
-        <v>-13188</v>
+        <v>-15740</v>
       </c>
       <c r="G75" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H75" s="2">
         <v>30</v>
       </c>
       <c r="I75" s="2">
-        <v>-10</v>
+        <v>30</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>15</v>
@@ -3372,22 +3363,22 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D76" s="2">
         <v>6157</v>
       </c>
       <c r="E76" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F76" s="2">
-        <v>-15304</v>
+        <v>-15303</v>
       </c>
       <c r="G76" s="2">
         <v>23</v>
@@ -3399,7 +3390,7 @@
         <v>7</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>15</v>
@@ -3407,34 +3398,34 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D77" s="2">
-        <v>6157</v>
+        <v>8901</v>
       </c>
       <c r="E77" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F77" s="2">
-        <v>-15304</v>
+        <v>-12559</v>
       </c>
       <c r="G77" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H77" s="2">
         <v>30</v>
       </c>
       <c r="I77" s="2">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>15</v>
@@ -3442,22 +3433,22 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D78" s="2">
-        <v>8095</v>
+        <v>8901</v>
       </c>
       <c r="E78" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F78" s="2">
-        <v>-13366</v>
+        <v>-12559</v>
       </c>
       <c r="G78" s="2">
         <v>46</v>
@@ -3469,7 +3460,7 @@
         <v>-16</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>15</v>
@@ -3477,22 +3468,22 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D79" s="2">
         <v>6157</v>
       </c>
       <c r="E79" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F79" s="2">
-        <v>-15304</v>
+        <v>-15303</v>
       </c>
       <c r="G79" s="2">
         <v>23</v>
@@ -3504,7 +3495,7 @@
         <v>7</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>15</v>
@@ -3512,22 +3503,22 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D80" s="2">
         <v>8095</v>
       </c>
       <c r="E80" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F80" s="2">
-        <v>-13366</v>
+        <v>-13365</v>
       </c>
       <c r="G80" s="2">
         <v>46</v>
@@ -3539,7 +3530,7 @@
         <v>-16</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>15</v>
@@ -3547,34 +3538,34 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D81" s="2">
-        <v>8095</v>
+        <v>8272</v>
       </c>
       <c r="E81" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F81" s="2">
-        <v>-13366</v>
+        <v>-13188</v>
       </c>
       <c r="G81" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H81" s="2">
         <v>30</v>
       </c>
       <c r="I81" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>15</v>
@@ -3582,34 +3573,34 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D82" s="2">
-        <v>8273</v>
+        <v>8901</v>
       </c>
       <c r="E82" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F82" s="2">
-        <v>-13188</v>
+        <v>-12559</v>
       </c>
       <c r="G82" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H82" s="2">
         <v>30</v>
       </c>
       <c r="I82" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>15</v>
@@ -3617,34 +3608,34 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D83" s="2">
-        <v>6157</v>
+        <v>8901</v>
       </c>
       <c r="E83" s="2">
-        <v>21461</v>
+        <v>9433</v>
       </c>
       <c r="F83" s="2">
-        <v>-15304</v>
+        <v>-532</v>
       </c>
       <c r="G83" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H83" s="2">
         <v>30</v>
       </c>
       <c r="I83" s="2">
-        <v>7</v>
-      </c>
-      <c r="J83" s="4" t="s">
-        <v>39</v>
+        <v>-16</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>15</v>
@@ -3655,31 +3646,31 @@
         <v>59</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D84" s="2">
-        <v>6744</v>
+        <v>5870</v>
       </c>
       <c r="E84" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F84" s="2">
-        <v>-14717</v>
+        <v>-15590</v>
       </c>
       <c r="G84" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H84" s="2">
         <v>30</v>
       </c>
       <c r="I84" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>15</v>
@@ -3690,31 +3681,31 @@
         <v>59</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="D85" s="2">
-        <v>8901</v>
+        <v>6157</v>
       </c>
       <c r="E85" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F85" s="2">
-        <v>-12560</v>
+        <v>-15303</v>
       </c>
       <c r="G85" s="2">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H85" s="2">
         <v>30</v>
       </c>
       <c r="I85" s="2">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K85" s="2" t="s">
         <v>15</v>
@@ -3725,19 +3716,19 @@
         <v>59</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D86" s="2">
         <v>8901</v>
       </c>
       <c r="E86" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F86" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G86" s="2">
         <v>46</v>
@@ -3749,7 +3740,7 @@
         <v>-16</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K86" s="2" t="s">
         <v>15</v>
@@ -3757,34 +3748,34 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D87" s="2">
-        <v>5870</v>
+        <v>8901</v>
       </c>
       <c r="E87" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F87" s="2">
-        <v>-15591</v>
+        <v>-12559</v>
       </c>
       <c r="G87" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H87" s="2">
         <v>30</v>
       </c>
       <c r="I87" s="2">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>15</v>
@@ -3795,19 +3786,19 @@
         <v>60</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D88" s="2">
         <v>6157</v>
       </c>
       <c r="E88" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F88" s="2">
-        <v>-15304</v>
+        <v>-15303</v>
       </c>
       <c r="G88" s="2">
         <v>23</v>
@@ -3819,7 +3810,7 @@
         <v>7</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>15</v>
@@ -3830,19 +3821,19 @@
         <v>60</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D89" s="2">
         <v>6157</v>
       </c>
       <c r="E89" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F89" s="2">
-        <v>-15304</v>
+        <v>-15303</v>
       </c>
       <c r="G89" s="2">
         <v>23</v>
@@ -3854,7 +3845,7 @@
         <v>7</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>15</v>
@@ -3865,19 +3856,19 @@
         <v>60</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D90" s="2">
         <v>8901</v>
       </c>
       <c r="E90" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F90" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G90" s="2">
         <v>46</v>
@@ -3889,7 +3880,7 @@
         <v>-16</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>15</v>
@@ -3900,31 +3891,31 @@
         <v>61</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D91" s="2">
-        <v>8901</v>
+        <v>6157</v>
       </c>
       <c r="E91" s="2">
-        <v>9433</v>
+        <v>21460</v>
       </c>
       <c r="F91" s="2">
-        <v>-532</v>
+        <v>-15303</v>
       </c>
       <c r="G91" s="2">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H91" s="2">
         <v>30</v>
       </c>
       <c r="I91" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="J91" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K91" s="2" t="s">
         <v>15</v>
@@ -3932,34 +3923,34 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D92" s="2">
-        <v>5870</v>
+        <v>8272</v>
       </c>
       <c r="E92" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F92" s="2">
-        <v>-15591</v>
+        <v>-13188</v>
       </c>
       <c r="G92" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H92" s="2">
         <v>30</v>
       </c>
       <c r="I92" s="2">
-        <v>30</v>
+        <v>-10</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K92" s="2" t="s">
         <v>15</v>
@@ -3967,34 +3958,34 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D93" s="2">
-        <v>6157</v>
+        <v>8901</v>
       </c>
       <c r="E93" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F93" s="2">
-        <v>-15304</v>
+        <v>-12559</v>
       </c>
       <c r="G93" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H93" s="2">
         <v>30</v>
       </c>
       <c r="I93" s="2">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>15</v>
@@ -4002,22 +3993,22 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D94" s="2">
-        <v>8095</v>
+        <v>8901</v>
       </c>
       <c r="E94" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F94" s="2">
-        <v>-13366</v>
+        <v>-12559</v>
       </c>
       <c r="G94" s="2">
         <v>46</v>
@@ -4029,7 +4020,7 @@
         <v>-16</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>15</v>
@@ -4040,31 +4031,31 @@
         <v>62</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D95" s="2">
-        <v>8901</v>
+        <v>5720</v>
       </c>
       <c r="E95" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F95" s="2">
-        <v>-12560</v>
+        <v>-15740</v>
       </c>
       <c r="G95" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H95" s="2">
         <v>30</v>
       </c>
       <c r="I95" s="2">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K95" s="2" t="s">
         <v>15</v>
@@ -4072,22 +4063,22 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D96" s="2">
         <v>6157</v>
       </c>
       <c r="E96" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F96" s="2">
-        <v>-15304</v>
+        <v>-15303</v>
       </c>
       <c r="G96" s="2">
         <v>23</v>
@@ -4099,7 +4090,7 @@
         <v>7</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K96" s="2" t="s">
         <v>15</v>
@@ -4107,34 +4098,34 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D97" s="2">
-        <v>6157</v>
+        <v>8901</v>
       </c>
       <c r="E97" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F97" s="2">
-        <v>-15304</v>
+        <v>-12559</v>
       </c>
       <c r="G97" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H97" s="2">
         <v>30</v>
       </c>
       <c r="I97" s="2">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K97" s="2" t="s">
         <v>15</v>
@@ -4142,22 +4133,22 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D98" s="2">
         <v>8901</v>
       </c>
       <c r="E98" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F98" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G98" s="2">
         <v>46</v>
@@ -4169,7 +4160,7 @@
         <v>-16</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K98" s="2" t="s">
         <v>15</v>
@@ -4177,10 +4168,10 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>29</v>
@@ -4189,10 +4180,10 @@
         <v>5870</v>
       </c>
       <c r="E99" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F99" s="2">
-        <v>-15591</v>
+        <v>-15590</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
@@ -4204,7 +4195,7 @@
         <v>30</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K99" s="2" t="s">
         <v>15</v>
@@ -4212,22 +4203,22 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D100" s="2">
         <v>6157</v>
       </c>
       <c r="E100" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F100" s="2">
-        <v>-15304</v>
+        <v>-15303</v>
       </c>
       <c r="G100" s="2">
         <v>23</v>
@@ -4239,7 +4230,7 @@
         <v>7</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>15</v>
@@ -4247,22 +4238,22 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D101" s="2">
         <v>8095</v>
       </c>
       <c r="E101" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F101" s="2">
-        <v>-13366</v>
+        <v>-13365</v>
       </c>
       <c r="G101" s="2">
         <v>46</v>
@@ -4274,7 +4265,7 @@
         <v>-16</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K101" s="2" t="s">
         <v>15</v>
@@ -4282,22 +4273,22 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D102" s="2">
         <v>8901</v>
       </c>
       <c r="E102" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F102" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G102" s="2">
         <v>46</v>
@@ -4309,7 +4300,7 @@
         <v>-16</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K102" s="2" t="s">
         <v>15</v>
@@ -4317,34 +4308,34 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D103" s="2">
-        <v>6157</v>
+        <v>8901</v>
       </c>
       <c r="E103" s="2">
-        <v>21461</v>
+        <v>9433</v>
       </c>
       <c r="F103" s="2">
-        <v>-15304</v>
+        <v>-532</v>
       </c>
       <c r="G103" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H103" s="2">
         <v>30</v>
       </c>
       <c r="I103" s="2">
-        <v>7</v>
-      </c>
-      <c r="J103" s="4" t="s">
-        <v>39</v>
+        <v>-16</v>
+      </c>
+      <c r="J103" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K103" s="2" t="s">
         <v>15</v>
@@ -4352,34 +4343,34 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="D104" s="2">
-        <v>6744</v>
+        <v>8901</v>
       </c>
       <c r="E104" s="2">
-        <v>21461</v>
+        <v>9433</v>
       </c>
       <c r="F104" s="2">
-        <v>-14717</v>
+        <v>-532</v>
       </c>
       <c r="G104" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H104" s="2">
         <v>30</v>
       </c>
       <c r="I104" s="2">
-        <v>10</v>
-      </c>
-      <c r="J104" s="4" t="s">
-        <v>39</v>
+        <v>-16</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K104" s="2" t="s">
         <v>15</v>
@@ -4390,31 +4381,31 @@
         <v>65</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D105" s="2">
-        <v>8901</v>
+        <v>5870</v>
       </c>
       <c r="E105" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F105" s="2">
-        <v>-12560</v>
+        <v>-15590</v>
       </c>
       <c r="G105" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H105" s="2">
         <v>30</v>
       </c>
       <c r="I105" s="2">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K105" s="2" t="s">
         <v>15</v>
@@ -4425,31 +4416,31 @@
         <v>65</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D106" s="2">
-        <v>8901</v>
+        <v>6157</v>
       </c>
       <c r="E106" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F106" s="2">
-        <v>-12560</v>
+        <v>-15303</v>
       </c>
       <c r="G106" s="2">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H106" s="2">
         <v>30</v>
       </c>
       <c r="I106" s="2">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>15</v>
@@ -4457,34 +4448,34 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D107" s="2">
-        <v>6157</v>
+        <v>8901</v>
       </c>
       <c r="E107" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F107" s="2">
-        <v>-15304</v>
+        <v>-12559</v>
       </c>
       <c r="G107" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H107" s="2">
         <v>30</v>
       </c>
       <c r="I107" s="2">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K107" s="2" t="s">
         <v>15</v>
@@ -4492,22 +4483,22 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D108" s="2">
-        <v>8095</v>
+        <v>8901</v>
       </c>
       <c r="E108" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F108" s="2">
-        <v>-13366</v>
+        <v>-12559</v>
       </c>
       <c r="G108" s="2">
         <v>46</v>
@@ -4519,7 +4510,7 @@
         <v>-16</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K108" s="2" t="s">
         <v>15</v>
@@ -4530,31 +4521,31 @@
         <v>66</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D109" s="2">
-        <v>8273</v>
+        <v>8095</v>
       </c>
       <c r="E109" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F109" s="2">
-        <v>-13188</v>
+        <v>-13365</v>
       </c>
       <c r="G109" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H109" s="2">
         <v>30</v>
       </c>
       <c r="I109" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K109" s="2" t="s">
         <v>15</v>
@@ -4565,19 +4556,19 @@
         <v>66</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D110" s="2">
         <v>8901</v>
       </c>
       <c r="E110" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F110" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G110" s="2">
         <v>46</v>
@@ -4589,7 +4580,7 @@
         <v>-16</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K110" s="2" t="s">
         <v>15</v>
@@ -4597,22 +4588,22 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D111" s="2">
         <v>8901</v>
       </c>
       <c r="E111" s="2">
-        <v>9433</v>
+        <v>21460</v>
       </c>
       <c r="F111" s="2">
-        <v>-532</v>
+        <v>-12559</v>
       </c>
       <c r="G111" s="2">
         <v>46</v>
@@ -4623,8 +4614,8 @@
       <c r="I111" s="2">
         <v>-16</v>
       </c>
-      <c r="J111" s="3" t="s">
-        <v>14</v>
+      <c r="J111" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K111" s="2" t="s">
         <v>15</v>
@@ -4635,31 +4626,31 @@
         <v>67</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D112" s="2">
-        <v>8901</v>
+        <v>5870</v>
       </c>
       <c r="E112" s="2">
-        <v>9433</v>
+        <v>21460</v>
       </c>
       <c r="F112" s="2">
-        <v>-532</v>
+        <v>-15590</v>
       </c>
       <c r="G112" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H112" s="2">
         <v>30</v>
       </c>
       <c r="I112" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J112" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J112" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K112" s="2" t="s">
         <v>15</v>
@@ -4667,34 +4658,34 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D113" s="2">
-        <v>5870</v>
+        <v>8901</v>
       </c>
       <c r="E113" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F113" s="2">
-        <v>-15591</v>
+        <v>-12559</v>
       </c>
       <c r="G113" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H113" s="2">
         <v>30</v>
       </c>
       <c r="I113" s="2">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K113" s="2" t="s">
         <v>15</v>
@@ -4702,34 +4693,34 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D114" s="2">
-        <v>6157</v>
+        <v>8901</v>
       </c>
       <c r="E114" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F114" s="2">
-        <v>-15304</v>
+        <v>-12559</v>
       </c>
       <c r="G114" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H114" s="2">
         <v>30</v>
       </c>
       <c r="I114" s="2">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K114" s="2" t="s">
         <v>15</v>
@@ -4737,22 +4728,22 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D115" s="2">
         <v>8901</v>
       </c>
       <c r="E115" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F115" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G115" s="2">
         <v>46</v>
@@ -4764,7 +4755,7 @@
         <v>-16</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K115" s="2" t="s">
         <v>15</v>
@@ -4775,31 +4766,31 @@
         <v>68</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="D116" s="2">
-        <v>8901</v>
+        <v>5720</v>
       </c>
       <c r="E116" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F116" s="2">
-        <v>-12560</v>
+        <v>-15740</v>
       </c>
       <c r="G116" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H116" s="2">
         <v>30</v>
       </c>
       <c r="I116" s="2">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J116" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K116" s="2" t="s">
         <v>15</v>
@@ -4807,34 +4798,34 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D117" s="2">
-        <v>8095</v>
+        <v>6157</v>
       </c>
       <c r="E117" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F117" s="2">
-        <v>-13366</v>
+        <v>-15303</v>
       </c>
       <c r="G117" s="2">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H117" s="2">
         <v>30</v>
       </c>
       <c r="I117" s="2">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J117" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K117" s="2" t="s">
         <v>15</v>
@@ -4842,22 +4833,22 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D118" s="2">
-        <v>8901</v>
+        <v>8095</v>
       </c>
       <c r="E118" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F118" s="2">
-        <v>-12560</v>
+        <v>-13365</v>
       </c>
       <c r="G118" s="2">
         <v>46</v>
@@ -4869,7 +4860,7 @@
         <v>-16</v>
       </c>
       <c r="J118" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K118" s="2" t="s">
         <v>15</v>
@@ -4877,22 +4868,22 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D119" s="2">
         <v>8901</v>
       </c>
       <c r="E119" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F119" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G119" s="2">
         <v>46</v>
@@ -4904,7 +4895,7 @@
         <v>-16</v>
       </c>
       <c r="J119" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K119" s="2" t="s">
         <v>15</v>
@@ -4912,10 +4903,10 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>29</v>
@@ -4924,10 +4915,10 @@
         <v>5870</v>
       </c>
       <c r="E120" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F120" s="2">
-        <v>-15591</v>
+        <v>-15590</v>
       </c>
       <c r="G120" s="2">
         <v>0</v>
@@ -4939,7 +4930,7 @@
         <v>30</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K120" s="2" t="s">
         <v>15</v>
@@ -4947,22 +4938,22 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D121" s="2">
-        <v>8901</v>
+        <v>8095</v>
       </c>
       <c r="E121" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F121" s="2">
-        <v>-12560</v>
+        <v>-13365</v>
       </c>
       <c r="G121" s="2">
         <v>46</v>
@@ -4974,7 +4965,7 @@
         <v>-16</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K121" s="2" t="s">
         <v>15</v>
@@ -4982,22 +4973,22 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D122" s="2">
-        <v>8901</v>
+        <v>8095</v>
       </c>
       <c r="E122" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F122" s="2">
-        <v>-12560</v>
+        <v>-13365</v>
       </c>
       <c r="G122" s="2">
         <v>46</v>
@@ -5009,7 +5000,7 @@
         <v>-16</v>
       </c>
       <c r="J122" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K122" s="2" t="s">
         <v>15</v>
@@ -5017,22 +5008,22 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D123" s="2">
         <v>8901</v>
       </c>
       <c r="E123" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F123" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G123" s="2">
         <v>46</v>
@@ -5044,7 +5035,7 @@
         <v>-16</v>
       </c>
       <c r="J123" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K123" s="2" t="s">
         <v>15</v>
@@ -5052,34 +5043,34 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D124" s="2">
-        <v>6157</v>
+        <v>8901</v>
       </c>
       <c r="E124" s="2">
-        <v>21461</v>
+        <v>9433</v>
       </c>
       <c r="F124" s="2">
-        <v>-15304</v>
+        <v>-532</v>
       </c>
       <c r="G124" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H124" s="2">
         <v>30</v>
       </c>
       <c r="I124" s="2">
-        <v>7</v>
-      </c>
-      <c r="J124" s="4" t="s">
-        <v>39</v>
+        <v>-16</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K124" s="2" t="s">
         <v>15</v>
@@ -5090,31 +5081,31 @@
         <v>71</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D125" s="2">
-        <v>6744</v>
+        <v>5870</v>
       </c>
       <c r="E125" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F125" s="2">
-        <v>-14717</v>
+        <v>-15590</v>
       </c>
       <c r="G125" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H125" s="2">
         <v>30</v>
       </c>
       <c r="I125" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K125" s="2" t="s">
         <v>15</v>
@@ -5125,19 +5116,19 @@
         <v>71</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D126" s="2">
         <v>8095</v>
       </c>
       <c r="E126" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F126" s="2">
-        <v>-13366</v>
+        <v>-13365</v>
       </c>
       <c r="G126" s="2">
         <v>46</v>
@@ -5149,7 +5140,7 @@
         <v>-16</v>
       </c>
       <c r="J126" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K126" s="2" t="s">
         <v>15</v>
@@ -5160,19 +5151,19 @@
         <v>71</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D127" s="2">
         <v>8901</v>
       </c>
       <c r="E127" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F127" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G127" s="2">
         <v>46</v>
@@ -5184,7 +5175,7 @@
         <v>-16</v>
       </c>
       <c r="J127" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K127" s="2" t="s">
         <v>15</v>
@@ -5192,34 +5183,34 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D128" s="2">
-        <v>5870</v>
+        <v>8901</v>
       </c>
       <c r="E128" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F128" s="2">
-        <v>-15591</v>
+        <v>-12559</v>
       </c>
       <c r="G128" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H128" s="2">
         <v>30</v>
       </c>
       <c r="I128" s="2">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J128" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K128" s="2" t="s">
         <v>15</v>
@@ -5230,19 +5221,19 @@
         <v>72</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D129" s="2">
-        <v>8095</v>
+        <v>8901</v>
       </c>
       <c r="E129" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F129" s="2">
-        <v>-13366</v>
+        <v>-12559</v>
       </c>
       <c r="G129" s="2">
         <v>46</v>
@@ -5254,7 +5245,7 @@
         <v>-16</v>
       </c>
       <c r="J129" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K129" s="2" t="s">
         <v>15</v>
@@ -5265,19 +5256,19 @@
         <v>72</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D130" s="2">
-        <v>8095</v>
+        <v>8901</v>
       </c>
       <c r="E130" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F130" s="2">
-        <v>-13366</v>
+        <v>-12559</v>
       </c>
       <c r="G130" s="2">
         <v>46</v>
@@ -5289,7 +5280,7 @@
         <v>-16</v>
       </c>
       <c r="J130" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>15</v>
@@ -5300,19 +5291,19 @@
         <v>72</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D131" s="2">
         <v>8901</v>
       </c>
       <c r="E131" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F131" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G131" s="2">
         <v>46</v>
@@ -5324,7 +5315,7 @@
         <v>-16</v>
       </c>
       <c r="J131" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K131" s="2" t="s">
         <v>15</v>
@@ -5335,31 +5326,31 @@
         <v>73</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D132" s="2">
-        <v>8901</v>
+        <v>8272</v>
       </c>
       <c r="E132" s="2">
-        <v>9433</v>
+        <v>21460</v>
       </c>
       <c r="F132" s="2">
-        <v>-532</v>
+        <v>-13188</v>
       </c>
       <c r="G132" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H132" s="2">
         <v>30</v>
       </c>
       <c r="I132" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J132" s="3" t="s">
-        <v>14</v>
+        <v>-10</v>
+      </c>
+      <c r="J132" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K132" s="2" t="s">
         <v>15</v>
@@ -5367,34 +5358,34 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D133" s="2">
-        <v>5870</v>
+        <v>8901</v>
       </c>
       <c r="E133" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F133" s="2">
-        <v>-15591</v>
+        <v>-12559</v>
       </c>
       <c r="G133" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H133" s="2">
         <v>30</v>
       </c>
       <c r="I133" s="2">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J133" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>15</v>
@@ -5402,22 +5393,22 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D134" s="2">
-        <v>8095</v>
+        <v>8901</v>
       </c>
       <c r="E134" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F134" s="2">
-        <v>-13366</v>
+        <v>-12559</v>
       </c>
       <c r="G134" s="2">
         <v>46</v>
@@ -5429,7 +5420,7 @@
         <v>-16</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K134" s="2" t="s">
         <v>15</v>
@@ -5437,22 +5428,22 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D135" s="2">
-        <v>8095</v>
+        <v>8901</v>
       </c>
       <c r="E135" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F135" s="2">
-        <v>-13366</v>
+        <v>-12559</v>
       </c>
       <c r="G135" s="2">
         <v>46</v>
@@ -5464,7 +5455,7 @@
         <v>-16</v>
       </c>
       <c r="J135" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K135" s="2" t="s">
         <v>15</v>
@@ -5475,31 +5466,31 @@
         <v>74</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D136" s="2">
-        <v>8901</v>
+        <v>7768</v>
       </c>
       <c r="E136" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F136" s="2">
-        <v>-12560</v>
+        <v>-13692</v>
       </c>
       <c r="G136" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H136" s="2">
         <v>30</v>
       </c>
       <c r="I136" s="2">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J136" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K136" s="2" t="s">
         <v>15</v>
@@ -5507,22 +5498,22 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D137" s="2">
         <v>8901</v>
       </c>
       <c r="E137" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F137" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G137" s="2">
         <v>46</v>
@@ -5534,7 +5525,7 @@
         <v>-16</v>
       </c>
       <c r="J137" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K137" s="2" t="s">
         <v>15</v>
@@ -5542,22 +5533,22 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="D138" s="2">
         <v>8901</v>
       </c>
       <c r="E138" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F138" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G138" s="2">
         <v>46</v>
@@ -5569,7 +5560,7 @@
         <v>-16</v>
       </c>
       <c r="J138" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K138" s="2" t="s">
         <v>15</v>
@@ -5577,22 +5568,22 @@
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D139" s="2">
         <v>8901</v>
       </c>
       <c r="E139" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F139" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G139" s="2">
         <v>46</v>
@@ -5604,7 +5595,7 @@
         <v>-16</v>
       </c>
       <c r="J139" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K139" s="2" t="s">
         <v>15</v>
@@ -5612,22 +5603,22 @@
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D140" s="2">
-        <v>8273</v>
+        <v>8272</v>
       </c>
       <c r="E140" s="2">
-        <v>21461</v>
+        <v>8286</v>
       </c>
       <c r="F140" s="2">
-        <v>-13188</v>
+        <v>-14</v>
       </c>
       <c r="G140" s="2">
         <v>40</v>
@@ -5638,8 +5629,8 @@
       <c r="I140" s="2">
         <v>-10</v>
       </c>
-      <c r="J140" s="4" t="s">
-        <v>39</v>
+      <c r="J140" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K140" s="2" t="s">
         <v>15</v>
@@ -5647,34 +5638,34 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D141" s="2">
-        <v>8901</v>
+        <v>8272</v>
       </c>
       <c r="E141" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F141" s="2">
-        <v>-12560</v>
+        <v>-13188</v>
       </c>
       <c r="G141" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H141" s="2">
         <v>30</v>
       </c>
       <c r="I141" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J141" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K141" s="2" t="s">
         <v>15</v>
@@ -5682,22 +5673,22 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D142" s="2">
         <v>8901</v>
       </c>
       <c r="E142" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F142" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G142" s="2">
         <v>46</v>
@@ -5709,7 +5700,7 @@
         <v>-16</v>
       </c>
       <c r="J142" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K142" s="2" t="s">
         <v>15</v>
@@ -5717,22 +5708,22 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D143" s="2">
         <v>8901</v>
       </c>
       <c r="E143" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F143" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G143" s="2">
         <v>46</v>
@@ -5744,7 +5735,7 @@
         <v>-16</v>
       </c>
       <c r="J143" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K143" s="2" t="s">
         <v>15</v>
@@ -5752,34 +5743,34 @@
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D144" s="2">
-        <v>8792</v>
+        <v>8901</v>
       </c>
       <c r="E144" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F144" s="2">
-        <v>-12669</v>
+        <v>-12559</v>
       </c>
       <c r="G144" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H144" s="2">
         <v>30</v>
       </c>
       <c r="I144" s="2">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J144" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K144" s="2" t="s">
         <v>15</v>
@@ -5787,22 +5778,22 @@
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D145" s="2">
         <v>8901</v>
       </c>
       <c r="E145" s="2">
-        <v>21461</v>
+        <v>9433</v>
       </c>
       <c r="F145" s="2">
-        <v>-12560</v>
+        <v>-532</v>
       </c>
       <c r="G145" s="2">
         <v>46</v>
@@ -5813,8 +5804,8 @@
       <c r="I145" s="2">
         <v>-16</v>
       </c>
-      <c r="J145" s="4" t="s">
-        <v>39</v>
+      <c r="J145" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K145" s="2" t="s">
         <v>15</v>
@@ -5825,31 +5816,31 @@
         <v>77</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D146" s="2">
-        <v>8901</v>
+        <v>5870</v>
       </c>
       <c r="E146" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F146" s="2">
-        <v>-12560</v>
+        <v>-15590</v>
       </c>
       <c r="G146" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H146" s="2">
         <v>30</v>
       </c>
       <c r="I146" s="2">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J146" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K146" s="2" t="s">
         <v>15</v>
@@ -5860,19 +5851,19 @@
         <v>77</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D147" s="2">
         <v>8901</v>
       </c>
       <c r="E147" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F147" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G147" s="2">
         <v>46</v>
@@ -5884,7 +5875,7 @@
         <v>-16</v>
       </c>
       <c r="J147" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K147" s="2" t="s">
         <v>15</v>
@@ -5892,34 +5883,34 @@
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D148" s="2">
-        <v>5870</v>
+        <v>8901</v>
       </c>
       <c r="E148" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F148" s="2">
-        <v>-15591</v>
+        <v>-12559</v>
       </c>
       <c r="G148" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H148" s="2">
         <v>30</v>
       </c>
       <c r="I148" s="2">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J148" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K148" s="2" t="s">
         <v>15</v>
@@ -5927,22 +5918,22 @@
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D149" s="2">
         <v>8901</v>
       </c>
       <c r="E149" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F149" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G149" s="2">
         <v>46</v>
@@ -5954,7 +5945,7 @@
         <v>-16</v>
       </c>
       <c r="J149" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K149" s="2" t="s">
         <v>15</v>
@@ -5965,19 +5956,19 @@
         <v>78</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D150" s="2">
-        <v>8901</v>
+        <v>8095</v>
       </c>
       <c r="E150" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F150" s="2">
-        <v>-12560</v>
+        <v>-13365</v>
       </c>
       <c r="G150" s="2">
         <v>46</v>
@@ -5989,7 +5980,7 @@
         <v>-16</v>
       </c>
       <c r="J150" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K150" s="2" t="s">
         <v>15</v>
@@ -6000,7 +5991,7 @@
         <v>78</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>17</v>
@@ -6009,10 +6000,10 @@
         <v>8901</v>
       </c>
       <c r="E151" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F151" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G151" s="2">
         <v>46</v>
@@ -6024,7 +6015,7 @@
         <v>-16</v>
       </c>
       <c r="J151" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K151" s="2" t="s">
         <v>15</v>
@@ -6032,22 +6023,22 @@
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D152" s="2">
         <v>8901</v>
       </c>
       <c r="E152" s="2">
-        <v>9433</v>
+        <v>21460</v>
       </c>
       <c r="F152" s="2">
-        <v>-532</v>
+        <v>-12559</v>
       </c>
       <c r="G152" s="2">
         <v>46</v>
@@ -6058,8 +6049,8 @@
       <c r="I152" s="2">
         <v>-16</v>
       </c>
-      <c r="J152" s="3" t="s">
-        <v>14</v>
+      <c r="J152" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K152" s="2" t="s">
         <v>15</v>
@@ -6067,10 +6058,10 @@
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>29</v>
@@ -6079,10 +6070,10 @@
         <v>5870</v>
       </c>
       <c r="E153" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F153" s="2">
-        <v>-15591</v>
+        <v>-15590</v>
       </c>
       <c r="G153" s="2">
         <v>0</v>
@@ -6094,7 +6085,7 @@
         <v>30</v>
       </c>
       <c r="J153" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K153" s="2" t="s">
         <v>15</v>
@@ -6102,22 +6093,22 @@
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D154" s="2">
         <v>8901</v>
       </c>
       <c r="E154" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F154" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G154" s="2">
         <v>46</v>
@@ -6129,7 +6120,7 @@
         <v>-16</v>
       </c>
       <c r="J154" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K154" s="2" t="s">
         <v>15</v>
@@ -6137,22 +6128,22 @@
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D155" s="2">
         <v>8901</v>
       </c>
       <c r="E155" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F155" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G155" s="2">
         <v>46</v>
@@ -6164,7 +6155,7 @@
         <v>-16</v>
       </c>
       <c r="J155" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K155" s="2" t="s">
         <v>15</v>
@@ -6172,22 +6163,22 @@
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D156" s="2">
         <v>8901</v>
       </c>
       <c r="E156" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F156" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G156" s="2">
         <v>46</v>
@@ -6199,7 +6190,7 @@
         <v>-16</v>
       </c>
       <c r="J156" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K156" s="2" t="s">
         <v>15</v>
@@ -6207,34 +6198,34 @@
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D157" s="2">
-        <v>8095</v>
+        <v>6744</v>
       </c>
       <c r="E157" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F157" s="2">
-        <v>-13366</v>
+        <v>-14716</v>
       </c>
       <c r="G157" s="2">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H157" s="2">
         <v>30</v>
       </c>
       <c r="I157" s="2">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J157" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K157" s="2" t="s">
         <v>15</v>
@@ -6242,22 +6233,22 @@
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D158" s="2">
         <v>8901</v>
       </c>
       <c r="E158" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F158" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G158" s="2">
         <v>46</v>
@@ -6269,7 +6260,7 @@
         <v>-16</v>
       </c>
       <c r="J158" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K158" s="2" t="s">
         <v>15</v>
@@ -6277,22 +6268,22 @@
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D159" s="2">
         <v>8901</v>
       </c>
       <c r="E159" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F159" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G159" s="2">
         <v>46</v>
@@ -6304,7 +6295,7 @@
         <v>-16</v>
       </c>
       <c r="J159" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K159" s="2" t="s">
         <v>15</v>
@@ -6312,34 +6303,34 @@
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D160" s="2">
-        <v>5870</v>
+        <v>8901</v>
       </c>
       <c r="E160" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F160" s="2">
-        <v>-15591</v>
+        <v>-12559</v>
       </c>
       <c r="G160" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H160" s="2">
         <v>30</v>
       </c>
       <c r="I160" s="2">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J160" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K160" s="2" t="s">
         <v>15</v>
@@ -6347,34 +6338,34 @@
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D161" s="2">
-        <v>8901</v>
+        <v>5870</v>
       </c>
       <c r="E161" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F161" s="2">
-        <v>-12560</v>
+        <v>-15590</v>
       </c>
       <c r="G161" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H161" s="2">
         <v>30</v>
       </c>
       <c r="I161" s="2">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J161" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K161" s="2" t="s">
         <v>15</v>
@@ -6382,22 +6373,22 @@
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D162" s="2">
-        <v>8901</v>
+        <v>8095</v>
       </c>
       <c r="E162" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F162" s="2">
-        <v>-12560</v>
+        <v>-13365</v>
       </c>
       <c r="G162" s="2">
         <v>46</v>
@@ -6409,7 +6400,7 @@
         <v>-16</v>
       </c>
       <c r="J162" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K162" s="2" t="s">
         <v>15</v>
@@ -6417,22 +6408,22 @@
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D163" s="2">
         <v>8901</v>
       </c>
       <c r="E163" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F163" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G163" s="2">
         <v>46</v>
@@ -6444,7 +6435,7 @@
         <v>-16</v>
       </c>
       <c r="J163" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K163" s="2" t="s">
         <v>15</v>
@@ -6452,34 +6443,34 @@
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D164" s="2">
-        <v>5720</v>
+        <v>8901</v>
       </c>
       <c r="E164" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F164" s="2">
-        <v>-15741</v>
+        <v>-12559</v>
       </c>
       <c r="G164" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H164" s="2">
         <v>30</v>
       </c>
       <c r="I164" s="2">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J164" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K164" s="2" t="s">
         <v>15</v>
@@ -6487,22 +6478,22 @@
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D165" s="2">
-        <v>8901</v>
+        <v>8095</v>
       </c>
       <c r="E165" s="2">
-        <v>21461</v>
+        <v>8778</v>
       </c>
       <c r="F165" s="2">
-        <v>-12560</v>
+        <v>-683</v>
       </c>
       <c r="G165" s="2">
         <v>46</v>
@@ -6513,8 +6504,8 @@
       <c r="I165" s="2">
         <v>-16</v>
       </c>
-      <c r="J165" s="4" t="s">
-        <v>39</v>
+      <c r="J165" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K165" s="2" t="s">
         <v>15</v>
@@ -6525,31 +6516,31 @@
         <v>83</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D166" s="2">
-        <v>8901</v>
+        <v>5870</v>
       </c>
       <c r="E166" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F166" s="2">
-        <v>-12560</v>
+        <v>-15590</v>
       </c>
       <c r="G166" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H166" s="2">
         <v>30</v>
       </c>
       <c r="I166" s="2">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J166" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K166" s="2" t="s">
         <v>15</v>
@@ -6560,19 +6551,19 @@
         <v>83</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="D167" s="2">
         <v>8901</v>
       </c>
       <c r="E167" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F167" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G167" s="2">
         <v>46</v>
@@ -6584,7 +6575,7 @@
         <v>-16</v>
       </c>
       <c r="J167" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K167" s="2" t="s">
         <v>15</v>
@@ -6592,34 +6583,34 @@
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D168" s="2">
-        <v>5870</v>
+        <v>8901</v>
       </c>
       <c r="E168" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F168" s="2">
-        <v>-15591</v>
+        <v>-12559</v>
       </c>
       <c r="G168" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H168" s="2">
         <v>30</v>
       </c>
       <c r="I168" s="2">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J168" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K168" s="2" t="s">
         <v>15</v>
@@ -6627,22 +6618,22 @@
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D169" s="2">
-        <v>8095</v>
+        <v>8901</v>
       </c>
       <c r="E169" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F169" s="2">
-        <v>-13366</v>
+        <v>-12559</v>
       </c>
       <c r="G169" s="2">
         <v>46</v>
@@ -6654,7 +6645,7 @@
         <v>-16</v>
       </c>
       <c r="J169" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K169" s="2" t="s">
         <v>15</v>
@@ -6665,19 +6656,19 @@
         <v>84</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D170" s="2">
         <v>8901</v>
       </c>
       <c r="E170" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F170" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G170" s="2">
         <v>46</v>
@@ -6689,7 +6680,7 @@
         <v>-16</v>
       </c>
       <c r="J170" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K170" s="2" t="s">
         <v>15</v>
@@ -6700,19 +6691,19 @@
         <v>84</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D171" s="2">
         <v>8901</v>
       </c>
       <c r="E171" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F171" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G171" s="2">
         <v>46</v>
@@ -6724,7 +6715,7 @@
         <v>-16</v>
       </c>
       <c r="J171" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K171" s="2" t="s">
         <v>15</v>
@@ -6732,22 +6723,22 @@
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="D172" s="2">
-        <v>8095</v>
+        <v>8901</v>
       </c>
       <c r="E172" s="2">
-        <v>8778</v>
+        <v>21460</v>
       </c>
       <c r="F172" s="2">
-        <v>-683</v>
+        <v>-12559</v>
       </c>
       <c r="G172" s="2">
         <v>46</v>
@@ -6758,8 +6749,8 @@
       <c r="I172" s="2">
         <v>-16</v>
       </c>
-      <c r="J172" s="3" t="s">
-        <v>14</v>
+      <c r="J172" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K172" s="2" t="s">
         <v>15</v>
@@ -6770,31 +6761,31 @@
         <v>85</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D173" s="2">
-        <v>8095</v>
+        <v>5870</v>
       </c>
       <c r="E173" s="2">
-        <v>8778</v>
+        <v>21460</v>
       </c>
       <c r="F173" s="2">
-        <v>-683</v>
+        <v>-15590</v>
       </c>
       <c r="G173" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H173" s="2">
         <v>30</v>
       </c>
       <c r="I173" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J173" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J173" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K173" s="2" t="s">
         <v>15</v>
@@ -6802,34 +6793,34 @@
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D174" s="2">
-        <v>5870</v>
+        <v>8095</v>
       </c>
       <c r="E174" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F174" s="2">
-        <v>-15591</v>
+        <v>-13365</v>
       </c>
       <c r="G174" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H174" s="2">
         <v>30</v>
       </c>
       <c r="I174" s="2">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J174" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K174" s="2" t="s">
         <v>15</v>
@@ -6837,22 +6828,22 @@
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D175" s="2">
         <v>8901</v>
       </c>
       <c r="E175" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F175" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G175" s="2">
         <v>46</v>
@@ -6864,7 +6855,7 @@
         <v>-16</v>
       </c>
       <c r="J175" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K175" s="2" t="s">
         <v>15</v>
@@ -6872,22 +6863,22 @@
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D176" s="2">
         <v>8901</v>
       </c>
       <c r="E176" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F176" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G176" s="2">
         <v>46</v>
@@ -6899,7 +6890,7 @@
         <v>-16</v>
       </c>
       <c r="J176" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K176" s="2" t="s">
         <v>15</v>
@@ -6910,31 +6901,31 @@
         <v>86</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="D177" s="2">
-        <v>8901</v>
+        <v>6744</v>
       </c>
       <c r="E177" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F177" s="2">
-        <v>-12560</v>
+        <v>-14716</v>
       </c>
       <c r="G177" s="2">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H177" s="2">
         <v>30</v>
       </c>
       <c r="I177" s="2">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J177" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K177" s="2" t="s">
         <v>15</v>
@@ -6942,22 +6933,22 @@
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D178" s="2">
         <v>8901</v>
       </c>
       <c r="E178" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F178" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G178" s="2">
         <v>46</v>
@@ -6969,7 +6960,7 @@
         <v>-16</v>
       </c>
       <c r="J178" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K178" s="2" t="s">
         <v>15</v>
@@ -6977,22 +6968,22 @@
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D179" s="2">
         <v>8901</v>
       </c>
       <c r="E179" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F179" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G179" s="2">
         <v>46</v>
@@ -7004,7 +6995,7 @@
         <v>-16</v>
       </c>
       <c r="J179" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K179" s="2" t="s">
         <v>15</v>
@@ -7012,22 +7003,22 @@
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D180" s="2">
         <v>8901</v>
       </c>
       <c r="E180" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F180" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G180" s="2">
         <v>46</v>
@@ -7039,7 +7030,7 @@
         <v>-16</v>
       </c>
       <c r="J180" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K180" s="2" t="s">
         <v>15</v>
@@ -7047,34 +7038,34 @@
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D181" s="2">
-        <v>8095</v>
+        <v>5870</v>
       </c>
       <c r="E181" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F181" s="2">
-        <v>-13366</v>
+        <v>-15590</v>
       </c>
       <c r="G181" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H181" s="2">
         <v>30</v>
       </c>
       <c r="I181" s="2">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J181" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K181" s="2" t="s">
         <v>15</v>
@@ -7082,34 +7073,34 @@
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D182" s="2">
-        <v>8273</v>
+        <v>8095</v>
       </c>
       <c r="E182" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F182" s="2">
-        <v>-13188</v>
+        <v>-13365</v>
       </c>
       <c r="G182" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H182" s="2">
         <v>30</v>
       </c>
       <c r="I182" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J182" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K182" s="2" t="s">
         <v>15</v>
@@ -7117,22 +7108,22 @@
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D183" s="2">
         <v>8901</v>
       </c>
       <c r="E183" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F183" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G183" s="2">
         <v>46</v>
@@ -7144,7 +7135,7 @@
         <v>-16</v>
       </c>
       <c r="J183" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K183" s="2" t="s">
         <v>15</v>
@@ -7152,22 +7143,22 @@
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D184" s="2">
         <v>8901</v>
       </c>
       <c r="E184" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F184" s="2">
-        <v>-12560</v>
+        <v>-12559</v>
       </c>
       <c r="G184" s="2">
         <v>46</v>
@@ -7179,7 +7170,7 @@
         <v>-16</v>
       </c>
       <c r="J184" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K184" s="2" t="s">
         <v>15</v>
@@ -7187,22 +7178,22 @@
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D185" s="2">
-        <v>5720</v>
+        <v>5870</v>
       </c>
       <c r="E185" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F185" s="2">
-        <v>-15741</v>
+        <v>-15590</v>
       </c>
       <c r="G185" s="2">
         <v>0</v>
@@ -7214,7 +7205,7 @@
         <v>30</v>
       </c>
       <c r="J185" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K185" s="2" t="s">
         <v>15</v>
@@ -7222,22 +7213,22 @@
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D186" s="2">
-        <v>8901</v>
+        <v>9720</v>
       </c>
       <c r="E186" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F186" s="2">
-        <v>-12560</v>
+        <v>-11740</v>
       </c>
       <c r="G186" s="2">
         <v>46</v>
@@ -7249,7 +7240,7 @@
         <v>-16</v>
       </c>
       <c r="J186" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K186" s="2" t="s">
         <v>15</v>
@@ -7257,22 +7248,22 @@
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D187" s="2">
-        <v>8901</v>
+        <v>9720</v>
       </c>
       <c r="E187" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F187" s="2">
-        <v>-12560</v>
+        <v>-11740</v>
       </c>
       <c r="G187" s="2">
         <v>46</v>
@@ -7284,7 +7275,7 @@
         <v>-16</v>
       </c>
       <c r="J187" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K187" s="2" t="s">
         <v>15</v>
@@ -7292,22 +7283,22 @@
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D188" s="2">
-        <v>8901</v>
+        <v>9720</v>
       </c>
       <c r="E188" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F188" s="2">
-        <v>-12560</v>
+        <v>-11740</v>
       </c>
       <c r="G188" s="2">
         <v>46</v>
@@ -7319,7 +7310,7 @@
         <v>-16</v>
       </c>
       <c r="J188" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K188" s="2" t="s">
         <v>15</v>
@@ -7327,22 +7318,22 @@
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D189" s="2">
-        <v>8095</v>
+        <v>9720</v>
       </c>
       <c r="E189" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F189" s="2">
-        <v>-13366</v>
+        <v>-11740</v>
       </c>
       <c r="G189" s="2">
         <v>46</v>
@@ -7354,7 +7345,7 @@
         <v>-16</v>
       </c>
       <c r="J189" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K189" s="2" t="s">
         <v>15</v>
@@ -7362,34 +7353,34 @@
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D190" s="2">
-        <v>8273</v>
+        <v>9720</v>
       </c>
       <c r="E190" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F190" s="2">
-        <v>-13188</v>
+        <v>-11740</v>
       </c>
       <c r="G190" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H190" s="2">
         <v>30</v>
       </c>
       <c r="I190" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J190" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K190" s="2" t="s">
         <v>15</v>
@@ -7397,22 +7388,22 @@
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D191" s="2">
-        <v>8901</v>
+        <v>9720</v>
       </c>
       <c r="E191" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F191" s="2">
-        <v>-12560</v>
+        <v>-11740</v>
       </c>
       <c r="G191" s="2">
         <v>46</v>
@@ -7424,7 +7415,7 @@
         <v>-16</v>
       </c>
       <c r="J191" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K191" s="2" t="s">
         <v>15</v>
@@ -7435,31 +7426,31 @@
         <v>90</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D192" s="2">
-        <v>8901</v>
+        <v>5870</v>
       </c>
       <c r="E192" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F192" s="2">
-        <v>-12560</v>
+        <v>-15590</v>
       </c>
       <c r="G192" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H192" s="2">
         <v>30</v>
       </c>
       <c r="I192" s="2">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J192" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K192" s="2" t="s">
         <v>15</v>
@@ -7467,34 +7458,34 @@
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D193" s="2">
-        <v>8273</v>
+        <v>9720</v>
       </c>
       <c r="E193" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F193" s="2">
-        <v>-13188</v>
+        <v>-11740</v>
       </c>
       <c r="G193" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H193" s="2">
         <v>30</v>
       </c>
       <c r="I193" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J193" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K193" s="2" t="s">
         <v>15</v>
@@ -7502,22 +7493,22 @@
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D194" s="2">
         <v>9720</v>
       </c>
       <c r="E194" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F194" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G194" s="2">
         <v>46</v>
@@ -7529,7 +7520,7 @@
         <v>-16</v>
       </c>
       <c r="J194" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K194" s="2" t="s">
         <v>15</v>
@@ -7537,22 +7528,22 @@
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D195" s="2">
         <v>9720</v>
       </c>
       <c r="E195" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F195" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G195" s="2">
         <v>46</v>
@@ -7564,7 +7555,7 @@
         <v>-16</v>
       </c>
       <c r="J195" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K195" s="2" t="s">
         <v>15</v>
@@ -7575,31 +7566,31 @@
         <v>91</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D196" s="2">
-        <v>9720</v>
+        <v>5720</v>
       </c>
       <c r="E196" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F196" s="2">
-        <v>-11741</v>
+        <v>-15740</v>
       </c>
       <c r="G196" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H196" s="2">
         <v>30</v>
       </c>
       <c r="I196" s="2">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J196" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K196" s="2" t="s">
         <v>15</v>
@@ -7607,22 +7598,22 @@
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D197" s="2">
         <v>9720</v>
       </c>
       <c r="E197" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F197" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G197" s="2">
         <v>46</v>
@@ -7634,7 +7625,7 @@
         <v>-16</v>
       </c>
       <c r="J197" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K197" s="2" t="s">
         <v>15</v>
@@ -7642,22 +7633,22 @@
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D198" s="2">
         <v>9720</v>
       </c>
       <c r="E198" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F198" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G198" s="2">
         <v>46</v>
@@ -7669,7 +7660,7 @@
         <v>-16</v>
       </c>
       <c r="J198" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K198" s="2" t="s">
         <v>15</v>
@@ -7677,22 +7668,22 @@
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D199" s="2">
         <v>9720</v>
       </c>
       <c r="E199" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F199" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G199" s="2">
         <v>46</v>
@@ -7704,7 +7695,7 @@
         <v>-16</v>
       </c>
       <c r="J199" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K199" s="2" t="s">
         <v>15</v>
@@ -7712,19 +7703,19 @@
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D200" s="2">
-        <v>8273</v>
+        <v>8272</v>
       </c>
       <c r="E200" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F200" s="2">
         <v>-13188</v>
@@ -7739,7 +7730,7 @@
         <v>-10</v>
       </c>
       <c r="J200" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K200" s="2" t="s">
         <v>15</v>
@@ -7747,22 +7738,22 @@
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D201" s="2">
         <v>9720</v>
       </c>
       <c r="E201" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F201" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G201" s="2">
         <v>46</v>
@@ -7774,7 +7765,7 @@
         <v>-16</v>
       </c>
       <c r="J201" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K201" s="2" t="s">
         <v>15</v>
@@ -7782,22 +7773,22 @@
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D202" s="2">
         <v>9720</v>
       </c>
       <c r="E202" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F202" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G202" s="2">
         <v>46</v>
@@ -7809,7 +7800,7 @@
         <v>-16</v>
       </c>
       <c r="J202" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K202" s="2" t="s">
         <v>15</v>
@@ -7817,22 +7808,22 @@
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D203" s="2">
         <v>9720</v>
       </c>
       <c r="E203" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F203" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G203" s="2">
         <v>46</v>
@@ -7844,7 +7835,7 @@
         <v>-16</v>
       </c>
       <c r="J203" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K203" s="2" t="s">
         <v>15</v>
@@ -7852,22 +7843,22 @@
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D204" s="2">
-        <v>5720</v>
+        <v>5870</v>
       </c>
       <c r="E204" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F204" s="2">
-        <v>-15741</v>
+        <v>-15590</v>
       </c>
       <c r="G204" s="2">
         <v>0</v>
@@ -7879,7 +7870,7 @@
         <v>30</v>
       </c>
       <c r="J204" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K204" s="2" t="s">
         <v>15</v>
@@ -7887,22 +7878,22 @@
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D205" s="2">
         <v>9720</v>
       </c>
       <c r="E205" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F205" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G205" s="2">
         <v>46</v>
@@ -7914,7 +7905,7 @@
         <v>-16</v>
       </c>
       <c r="J205" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K205" s="2" t="s">
         <v>15</v>
@@ -7922,22 +7913,22 @@
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D206" s="2">
         <v>9720</v>
       </c>
       <c r="E206" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F206" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G206" s="2">
         <v>46</v>
@@ -7949,7 +7940,7 @@
         <v>-16</v>
       </c>
       <c r="J206" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K206" s="2" t="s">
         <v>15</v>
@@ -7957,22 +7948,22 @@
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D207" s="2">
         <v>9720</v>
       </c>
       <c r="E207" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F207" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G207" s="2">
         <v>46</v>
@@ -7984,7 +7975,7 @@
         <v>-16</v>
       </c>
       <c r="J207" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K207" s="2" t="s">
         <v>15</v>
@@ -7992,34 +7983,34 @@
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D208" s="2">
-        <v>8273</v>
+        <v>9720</v>
       </c>
       <c r="E208" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F208" s="2">
-        <v>-13188</v>
+        <v>-11740</v>
       </c>
       <c r="G208" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H208" s="2">
         <v>30</v>
       </c>
       <c r="I208" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J208" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K208" s="2" t="s">
         <v>15</v>
@@ -8027,22 +8018,22 @@
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D209" s="2">
         <v>9720</v>
       </c>
       <c r="E209" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F209" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G209" s="2">
         <v>46</v>
@@ -8054,7 +8045,7 @@
         <v>-16</v>
       </c>
       <c r="J209" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K209" s="2" t="s">
         <v>15</v>
@@ -8062,22 +8053,22 @@
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D210" s="2">
         <v>9720</v>
       </c>
       <c r="E210" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F210" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G210" s="2">
         <v>46</v>
@@ -8089,7 +8080,7 @@
         <v>-16</v>
       </c>
       <c r="J210" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K210" s="2" t="s">
         <v>15</v>
@@ -8100,31 +8091,31 @@
         <v>95</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D211" s="2">
-        <v>9720</v>
+        <v>5870</v>
       </c>
       <c r="E211" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F211" s="2">
-        <v>-11741</v>
+        <v>-15590</v>
       </c>
       <c r="G211" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H211" s="2">
         <v>30</v>
       </c>
       <c r="I211" s="2">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J211" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K211" s="2" t="s">
         <v>15</v>
@@ -8132,34 +8123,34 @@
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D212" s="2">
-        <v>8273</v>
+        <v>9720</v>
       </c>
       <c r="E212" s="2">
-        <v>8778</v>
+        <v>21460</v>
       </c>
       <c r="F212" s="2">
-        <v>-505</v>
+        <v>-11740</v>
       </c>
       <c r="G212" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H212" s="2">
         <v>30</v>
       </c>
       <c r="I212" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J212" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J212" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K212" s="2" t="s">
         <v>15</v>
@@ -8167,34 +8158,34 @@
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D213" s="2">
-        <v>8273</v>
+        <v>9720</v>
       </c>
       <c r="E213" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F213" s="2">
-        <v>-13188</v>
+        <v>-11740</v>
       </c>
       <c r="G213" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H213" s="2">
         <v>30</v>
       </c>
       <c r="I213" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J213" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K213" s="2" t="s">
         <v>15</v>
@@ -8202,22 +8193,22 @@
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D214" s="2">
         <v>9720</v>
       </c>
       <c r="E214" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F214" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G214" s="2">
         <v>46</v>
@@ -8229,7 +8220,7 @@
         <v>-16</v>
       </c>
       <c r="J214" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K214" s="2" t="s">
         <v>15</v>
@@ -8240,31 +8231,31 @@
         <v>96</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D215" s="2">
-        <v>9720</v>
+        <v>8587</v>
       </c>
       <c r="E215" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F215" s="2">
-        <v>-11741</v>
+        <v>-12873</v>
       </c>
       <c r="G215" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H215" s="2">
         <v>30</v>
       </c>
       <c r="I215" s="2">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J215" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K215" s="2" t="s">
         <v>15</v>
@@ -8275,19 +8266,19 @@
         <v>96</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D216" s="2">
         <v>9720</v>
       </c>
       <c r="E216" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F216" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G216" s="2">
         <v>46</v>
@@ -8299,7 +8290,7 @@
         <v>-16</v>
       </c>
       <c r="J216" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K216" s="2" t="s">
         <v>15</v>
@@ -8307,22 +8298,22 @@
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D217" s="2">
         <v>9720</v>
       </c>
       <c r="E217" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F217" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G217" s="2">
         <v>46</v>
@@ -8334,7 +8325,7 @@
         <v>-16</v>
       </c>
       <c r="J217" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K217" s="2" t="s">
         <v>15</v>
@@ -8342,22 +8333,22 @@
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D218" s="2">
         <v>9720</v>
       </c>
       <c r="E218" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F218" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G218" s="2">
         <v>46</v>
@@ -8369,7 +8360,7 @@
         <v>-16</v>
       </c>
       <c r="J218" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K218" s="2" t="s">
         <v>15</v>
@@ -8380,31 +8371,31 @@
         <v>97</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D219" s="2">
-        <v>9720</v>
+        <v>5870</v>
       </c>
       <c r="E219" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F219" s="2">
-        <v>-11741</v>
+        <v>-15590</v>
       </c>
       <c r="G219" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H219" s="2">
         <v>30</v>
       </c>
       <c r="I219" s="2">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J219" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K219" s="2" t="s">
         <v>15</v>
@@ -8412,34 +8403,34 @@
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D220" s="2">
-        <v>5870</v>
+        <v>9720</v>
       </c>
       <c r="E220" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F220" s="2">
-        <v>-15591</v>
+        <v>-11740</v>
       </c>
       <c r="G220" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H220" s="2">
         <v>30</v>
       </c>
       <c r="I220" s="2">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J220" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K220" s="2" t="s">
         <v>15</v>
@@ -8447,22 +8438,22 @@
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D221" s="2">
         <v>9720</v>
       </c>
       <c r="E221" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F221" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G221" s="2">
         <v>46</v>
@@ -8474,7 +8465,7 @@
         <v>-16</v>
       </c>
       <c r="J221" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K221" s="2" t="s">
         <v>15</v>
@@ -8482,10 +8473,10 @@
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>28</v>
@@ -8494,10 +8485,10 @@
         <v>9720</v>
       </c>
       <c r="E222" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F222" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G222" s="2">
         <v>46</v>
@@ -8509,7 +8500,7 @@
         <v>-16</v>
       </c>
       <c r="J222" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K222" s="2" t="s">
         <v>15</v>
@@ -8520,31 +8511,31 @@
         <v>98</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D223" s="2">
-        <v>9720</v>
+        <v>8272</v>
       </c>
       <c r="E223" s="2">
-        <v>21461</v>
+        <v>8778</v>
       </c>
       <c r="F223" s="2">
-        <v>-11741</v>
+        <v>-506</v>
       </c>
       <c r="G223" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H223" s="2">
         <v>30</v>
       </c>
       <c r="I223" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J223" s="4" t="s">
-        <v>39</v>
+        <v>-10</v>
+      </c>
+      <c r="J223" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K223" s="2" t="s">
         <v>15</v>
@@ -8552,34 +8543,34 @@
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D224" s="2">
-        <v>9611</v>
+        <v>8272</v>
       </c>
       <c r="E224" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F224" s="2">
-        <v>-11850</v>
+        <v>-13188</v>
       </c>
       <c r="G224" s="2">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H224" s="2">
         <v>30</v>
       </c>
       <c r="I224" s="2">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="J224" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K224" s="2" t="s">
         <v>15</v>
@@ -8587,22 +8578,22 @@
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D225" s="2">
         <v>9720</v>
       </c>
       <c r="E225" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F225" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G225" s="2">
         <v>46</v>
@@ -8614,7 +8605,7 @@
         <v>-16</v>
       </c>
       <c r="J225" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K225" s="2" t="s">
         <v>15</v>
@@ -8622,22 +8613,22 @@
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D226" s="2">
         <v>9720</v>
       </c>
       <c r="E226" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F226" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G226" s="2">
         <v>46</v>
@@ -8649,7 +8640,7 @@
         <v>-16</v>
       </c>
       <c r="J226" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K226" s="2" t="s">
         <v>15</v>
@@ -8657,10 +8648,10 @@
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>28</v>
@@ -8669,10 +8660,10 @@
         <v>9720</v>
       </c>
       <c r="E227" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F227" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G227" s="2">
         <v>46</v>
@@ -8684,7 +8675,7 @@
         <v>-16</v>
       </c>
       <c r="J227" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K227" s="2" t="s">
         <v>15</v>
@@ -8692,34 +8683,34 @@
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D228" s="2">
-        <v>8273</v>
+        <v>9720</v>
       </c>
       <c r="E228" s="2">
-        <v>8778</v>
+        <v>21460</v>
       </c>
       <c r="F228" s="2">
-        <v>-505</v>
+        <v>-11740</v>
       </c>
       <c r="G228" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H228" s="2">
         <v>30</v>
       </c>
       <c r="I228" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J228" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J228" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="K228" s="2" t="s">
         <v>15</v>
@@ -8727,34 +8718,34 @@
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D229" s="2">
-        <v>8273</v>
+        <v>9720</v>
       </c>
       <c r="E229" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F229" s="2">
-        <v>-13188</v>
+        <v>-11740</v>
       </c>
       <c r="G229" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H229" s="2">
         <v>30</v>
       </c>
       <c r="I229" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J229" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K229" s="2" t="s">
         <v>15</v>
@@ -8762,22 +8753,22 @@
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D230" s="2">
         <v>9720</v>
       </c>
       <c r="E230" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F230" s="2">
-        <v>-11741</v>
+        <v>-11740</v>
       </c>
       <c r="G230" s="2">
         <v>46</v>
@@ -8789,324 +8780,9 @@
         <v>-16</v>
       </c>
       <c r="J230" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K230" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A231" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D231" s="2">
-        <v>9720</v>
-      </c>
-      <c r="E231" s="2">
-        <v>21461</v>
-      </c>
-      <c r="F231" s="2">
-        <v>-11741</v>
-      </c>
-      <c r="G231" s="2">
-        <v>46</v>
-      </c>
-      <c r="H231" s="2">
-        <v>30</v>
-      </c>
-      <c r="I231" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J231" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K231" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A232" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D232" s="2">
-        <v>9720</v>
-      </c>
-      <c r="E232" s="2">
-        <v>21461</v>
-      </c>
-      <c r="F232" s="2">
-        <v>-11741</v>
-      </c>
-      <c r="G232" s="2">
-        <v>46</v>
-      </c>
-      <c r="H232" s="2">
-        <v>30</v>
-      </c>
-      <c r="I232" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J232" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K232" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A233" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D233" s="2">
-        <v>5870</v>
-      </c>
-      <c r="E233" s="2">
-        <v>21461</v>
-      </c>
-      <c r="F233" s="2">
-        <v>-15591</v>
-      </c>
-      <c r="G233" s="2">
-        <v>0</v>
-      </c>
-      <c r="H233" s="2">
-        <v>30</v>
-      </c>
-      <c r="I233" s="2">
-        <v>30</v>
-      </c>
-      <c r="J233" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K233" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A234" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D234" s="2">
-        <v>9720</v>
-      </c>
-      <c r="E234" s="2">
-        <v>21461</v>
-      </c>
-      <c r="F234" s="2">
-        <v>-11741</v>
-      </c>
-      <c r="G234" s="2">
-        <v>46</v>
-      </c>
-      <c r="H234" s="2">
-        <v>30</v>
-      </c>
-      <c r="I234" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J234" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K234" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A235" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D235" s="2">
-        <v>9720</v>
-      </c>
-      <c r="E235" s="2">
-        <v>21461</v>
-      </c>
-      <c r="F235" s="2">
-        <v>-11741</v>
-      </c>
-      <c r="G235" s="2">
-        <v>46</v>
-      </c>
-      <c r="H235" s="2">
-        <v>30</v>
-      </c>
-      <c r="I235" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J235" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K235" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A236" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D236" s="2">
-        <v>9720</v>
-      </c>
-      <c r="E236" s="2">
-        <v>21461</v>
-      </c>
-      <c r="F236" s="2">
-        <v>-11741</v>
-      </c>
-      <c r="G236" s="2">
-        <v>46</v>
-      </c>
-      <c r="H236" s="2">
-        <v>30</v>
-      </c>
-      <c r="I236" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J236" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K236" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A237" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B237" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D237" s="2">
-        <v>9720</v>
-      </c>
-      <c r="E237" s="2">
-        <v>21461</v>
-      </c>
-      <c r="F237" s="2">
-        <v>-11741</v>
-      </c>
-      <c r="G237" s="2">
-        <v>46</v>
-      </c>
-      <c r="H237" s="2">
-        <v>30</v>
-      </c>
-      <c r="I237" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J237" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K237" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A238" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D238" s="2">
-        <v>9720</v>
-      </c>
-      <c r="E238" s="2">
-        <v>21461</v>
-      </c>
-      <c r="F238" s="2">
-        <v>-11741</v>
-      </c>
-      <c r="G238" s="2">
-        <v>46</v>
-      </c>
-      <c r="H238" s="2">
-        <v>30</v>
-      </c>
-      <c r="I238" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J238" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K238" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A239" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B239" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D239" s="2">
-        <v>9720</v>
-      </c>
-      <c r="E239" s="2">
-        <v>21461</v>
-      </c>
-      <c r="F239" s="2">
-        <v>-11741</v>
-      </c>
-      <c r="G239" s="2">
-        <v>46</v>
-      </c>
-      <c r="H239" s="2">
-        <v>30</v>
-      </c>
-      <c r="I239" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J239" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K239" s="2" t="s">
         <v>15</v>
       </c>
     </row>
